--- a/12_Equity_Finance/instances/public_tesla_2020_offering.xlsx
+++ b/12_Equity_Finance/instances/public_tesla_2020_offering.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cap Table &amp; Dilution" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Rights Offering" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Convertible Securities" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Decision &amp; Checks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="IS" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="BS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="CF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="DCF" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Comps" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="RefreshLog" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap Table &amp; Dilution" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rights Offering" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convertible Securities" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision &amp; Checks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
@@ -35,14 +35,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0x"/>
-    <numFmt numFmtId="168" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0x"/>
+    <numFmt numFmtId="169" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -180,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,32 +196,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -232,10 +234,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -601,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D20"/>
+  <dimension ref="B1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -610,6 +615,7 @@
     <col width="4" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -617,15 +623,16 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Issuer / security:</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>[fill in]</t>
+      <c r="C4" s="45" t="inlineStr">
+        <is>
+          <t>Tesla February 2020 underwritten primary offering</t>
         </is>
       </c>
     </row>
@@ -647,7 +654,7 @@
           <t>Last refreshed:</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>2020-02-14</t>
         </is>
@@ -677,6 +684,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -694,6 +702,7 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -833,22 +842,28 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12">
+      <c r="C5" s="49" t="n">
+        <v>11759</v>
+      </c>
+      <c r="D5" s="49" t="n">
+        <v>21461</v>
+      </c>
+      <c r="E5" s="49" t="n">
+        <v>24578</v>
+      </c>
+      <c r="F5" s="13">
         <f>E5*(1+Assumptions!C5)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <f>F5*(1+Assumptions!D5)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <f>G5*(1+Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <f>H5*(1+Assumptions!F5)</f>
         <v/>
       </c>
@@ -859,28 +874,28 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13">
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14">
         <f>IFERROR(D5/C5-1,"-")</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>IFERROR(E5/D5-1,"-")</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>IFERROR(F5/E5-1,"-")</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>IFERROR(G5/F5-1,"-")</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>IFERROR(H5/G5-1,"-")</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>IFERROR(I5/H5-1,"-")</f>
         <v/>
       </c>
@@ -891,22 +906,28 @@
           <t>COGS</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12">
+      <c r="C7" s="49" t="n">
+        <v>9536</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <v>17419</v>
+      </c>
+      <c r="E7" s="49" t="n">
+        <v>20509</v>
+      </c>
+      <c r="F7" s="13">
         <f>F5*(1-Assumptions!C6)</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>G5*(1-Assumptions!D6)</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <f>H5*(1-Assumptions!E6)</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <f>I5*(1-Assumptions!F6)</f>
         <v/>
       </c>
@@ -917,28 +938,31 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12">
+      <c r="C8" s="13">
+        <f>C5-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="13">
         <f>D5-D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5-E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5-F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5-G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>H5-H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <f>I5-I7</f>
         <v/>
       </c>
@@ -949,28 +973,31 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13">
+      <c r="C9" s="14">
+        <f>IFERROR(C8/C5,"-")</f>
+        <v/>
+      </c>
+      <c r="D9" s="14">
         <f>IFERROR(D8/D5,"-")</f>
         <v/>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <f>IFERROR(E8/E5,"-")</f>
         <v/>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>IFERROR(F8/F5,"-")</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>IFERROR(G8/G5,"-")</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f>IFERROR(H8/H5,"-")</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="14">
         <f>IFERROR(I8/I5,"-")</f>
         <v/>
       </c>
@@ -981,22 +1008,28 @@
           <t>Opex</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12">
+      <c r="C10" s="49" t="n">
+        <v>2219</v>
+      </c>
+      <c r="D10" s="49" t="n">
+        <v>2529</v>
+      </c>
+      <c r="E10" s="49" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F10" s="13">
         <f>F5*Assumptions!C7</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G5*Assumptions!D7</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <f>H5*Assumptions!E7</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <f>I5*Assumptions!F7</f>
         <v/>
       </c>
@@ -1007,22 +1040,31 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12">
+      <c r="C11" s="13">
+        <f>C8-C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="13">
+        <f>D8-D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="13">
+        <f>E8-E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
         <f>F8-F10</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>G8-G10</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <f>H8-H10</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <f>I8-I10</f>
         <v/>
       </c>
@@ -1033,22 +1075,31 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13">
+      <c r="C12" s="14">
+        <f>IFERROR(C11/C5,"-")</f>
+        <v/>
+      </c>
+      <c r="D12" s="14">
+        <f>IFERROR(D11/D5,"-")</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>IFERROR(E11/E5,"-")</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
         <f>IFERROR(F11/F5,"-")</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>IFERROR(G11/G5,"-")</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <f>IFERROR(H11/H5,"-")</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="14">
         <f>IFERROR(I11/I5,"-")</f>
         <v/>
       </c>
@@ -1059,22 +1110,28 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12">
+      <c r="C13" s="49" t="n">
+        <v>1636</v>
+      </c>
+      <c r="D13" s="49" t="n">
+        <v>1901</v>
+      </c>
+      <c r="E13" s="49" t="n">
+        <v>2154</v>
+      </c>
+      <c r="F13" s="13">
         <f>F5*Assumptions!C10*Assumptions!C9</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>G5*Assumptions!D10*Assumptions!D9</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>H5*Assumptions!E10*Assumptions!E9</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <f>I5*Assumptions!F10*Assumptions!F9</f>
         <v/>
       </c>
@@ -1085,22 +1142,31 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12">
+      <c r="C14" s="13">
+        <f>C11-C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>D11-D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="13">
+        <f>E11-E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="13">
         <f>F11-F13</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>G11-G13</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <f>H11-H13</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <f>I11-I13</f>
         <v/>
       </c>
@@ -1111,22 +1177,28 @@
           <t>Interest expense</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12">
+      <c r="C15" s="49" t="n">
+        <v>471</v>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>663</v>
+      </c>
+      <c r="E15" s="49" t="n">
+        <v>685</v>
+      </c>
+      <c r="F15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
@@ -1137,22 +1209,31 @@
           <t>Pre-tax income</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12">
+      <c r="C16" s="13">
+        <f>C14-C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="13">
+        <f>D14-D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="13">
+        <f>E14-E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="13">
         <f>F14-F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>G14-G15</f>
         <v/>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <f>H14-H15</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <f>I14-I15</f>
         <v/>
       </c>
@@ -1163,22 +1244,28 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12">
+      <c r="C17" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="D17" s="49" t="n">
+        <v>58</v>
+      </c>
+      <c r="E17" s="49" t="n">
+        <v>110</v>
+      </c>
+      <c r="F17" s="13">
         <f>F16*Assumptions!C8</f>
         <v/>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <f>G16*Assumptions!D8</f>
         <v/>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <f>H16*Assumptions!E8</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <f>I16*Assumptions!F8</f>
         <v/>
       </c>
@@ -1189,22 +1276,31 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12">
+      <c r="C18" s="13">
+        <f>C16-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="13">
+        <f>D16-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="13">
+        <f>E16-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="13">
         <f>F16-F17</f>
         <v/>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <f>G16-G17</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <f>H16-H17</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <f>I16-I17</f>
         <v/>
       </c>
@@ -1215,22 +1311,28 @@
           <t>Diluted shares</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12">
+      <c r="C19" s="50" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="D19" s="50" t="n">
+        <v>173</v>
+      </c>
+      <c r="E19" s="50" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="F19" s="13">
         <f>Assumptions!C12</f>
         <v/>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <f>Assumptions!D12</f>
         <v/>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <f>Assumptions!E12</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <f>Assumptions!F12</f>
         <v/>
       </c>
@@ -1241,22 +1343,31 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12">
+      <c r="C20" s="13">
+        <f>IFERROR(C18/C19,"-")</f>
+        <v/>
+      </c>
+      <c r="D20" s="13">
+        <f>IFERROR(D18/D19,"-")</f>
+        <v/>
+      </c>
+      <c r="E20" s="13">
+        <f>IFERROR(E18/E19,"-")</f>
+        <v/>
+      </c>
+      <c r="F20" s="13">
         <f>IFERROR(F18/F19,"-")</f>
         <v/>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <f>IFERROR(G18/G19,"-")</f>
         <v/>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <f>IFERROR(H18/H19,"-")</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <f>IFERROR(I18/I19,"-")</f>
         <v/>
       </c>
@@ -1330,11 +1441,11 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -1342,11 +1453,11 @@
           <t>Accounts receivable</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -1354,11 +1465,11 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -1366,23 +1477,23 @@
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -1393,11 +1504,11 @@
           <t>PP&amp;E net</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -1405,11 +1516,11 @@
           <t>Goodwill &amp; intangibles</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -1417,23 +1528,23 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <f>C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <f>D8+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>G8+G9+G10</f>
         <v/>
       </c>
@@ -1444,11 +1555,11 @@
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -1456,11 +1567,11 @@
           <t>Debt (current)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -1468,23 +1579,23 @@
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="13">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <f>E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>G12+G13</f>
         <v/>
       </c>
@@ -1495,11 +1606,11 @@
           <t>Long-term debt</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -1507,23 +1618,23 @@
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="13">
         <f>C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="13">
         <f>D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <f>E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>G14+G15</f>
         <v/>
       </c>
@@ -1534,35 +1645,35 @@
           <t>Total equity</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Balance check (Total assets - Total liabilities - Total equity, should = 0)</t>
         </is>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="17">
         <f>C11-C16-C17</f>
         <v/>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="17">
         <f>D11-D16-D17</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="17">
         <f>E11-E16-E17</f>
         <v/>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="17">
         <f>F11-F16-F17</f>
         <v/>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="17">
         <f>G11-G16-G17</f>
         <v/>
       </c>
@@ -1636,17 +1747,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="16">
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="18">
         <f>IS!F18</f>
         <v/>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="18">
         <f>IS!G18</f>
         <v/>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="18">
         <f>IS!H18</f>
         <v/>
       </c>
@@ -1657,17 +1768,17 @@
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="16">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="18">
         <f>IS!F13</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="18">
         <f>IS!G13</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="18">
         <f>IS!H13</f>
         <v/>
       </c>
@@ -1678,11 +1789,11 @@
           <t>+/- Change in NWC</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -1690,23 +1801,23 @@
           <t>Cash flow from operations</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -1717,11 +1828,11 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -1729,23 +1840,23 @@
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="13">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G8+G9</f>
         <v/>
       </c>
@@ -1756,11 +1867,11 @@
           <t>Debt issuance/(repayment)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -1768,11 +1879,11 @@
           <t>Dividends/buybacks</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -1780,23 +1891,23 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="13">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>G10+G11+G12</f>
         <v/>
       </c>
@@ -1872,23 +1983,23 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="19">
         <f>IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="19">
         <f>IS!G14*(1-Assumptions!D8)+IS!G13-IS!G5*Assumptions!D10</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="19">
         <f>IS!H14*(1-Assumptions!E8)+IS!H13-IS!H5*Assumptions!E10</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="19">
         <f>IS!I14*(1-Assumptions!F8)+IS!I13-IS!I5*Assumptions!F10</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="19">
         <f>F5*(1+Assumptions!G5)</f>
         <v/>
       </c>
@@ -1897,8 +2008,8 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="I5" s="18" t="n">
-        <v>0.1</v>
+      <c r="I5" s="51" t="n">
+        <v>0.095</v>
       </c>
     </row>
     <row r="6">
@@ -1907,23 +2018,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="21">
         <f>1/(1+$I$5)^(1)</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="21">
         <f>1/(1+$I$5)^(2)</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="21">
         <f>1/(1+$I$5)^(3)</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="21">
         <f>1/(1+$I$5)^(4)</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="21">
         <f>1/(1+$I$5)^(5)</f>
         <v/>
       </c>
@@ -1932,7 +2043,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="51" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1942,23 +2053,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="22">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f>F5*F6</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <f>G5*G6</f>
         <v/>
       </c>
@@ -1967,7 +2078,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="22">
         <f>G5*(1+I6)/(I5-I6)</f>
         <v/>
       </c>
@@ -1978,7 +2089,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="22">
         <f>I7*G6</f>
         <v/>
       </c>
@@ -1989,7 +2100,7 @@
           <t>Sum PV of FCF</t>
         </is>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="22">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
@@ -2000,7 +2111,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="23">
         <f>I8+I9</f>
         <v/>
       </c>
@@ -2011,8 +2122,8 @@
           <t>Less: net debt</t>
         </is>
       </c>
-      <c r="I11" s="22" t="n">
-        <v>0</v>
+      <c r="I11" s="52" t="n">
+        <v>-6105</v>
       </c>
     </row>
     <row r="12">
@@ -2021,7 +2132,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="23">
         <f>I10-I11</f>
         <v/>
       </c>
@@ -2032,8 +2143,8 @@
           <t>Diluted shares (mm)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="n">
-        <v>1</v>
+      <c r="I13" s="52" t="n">
+        <v>179.7</v>
       </c>
     </row>
     <row r="14">
@@ -2042,7 +2153,7 @@
           <t>Implied value/share</t>
         </is>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="23">
         <f>I12/I13</f>
         <v/>
       </c>
@@ -2131,13 +2242,13 @@
       <c r="E5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="23" t="n">
+      <c r="H5" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2156,13 +2267,13 @@
       <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="23" t="n">
+      <c r="H6" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2181,13 +2292,13 @@
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="23" t="n">
+      <c r="H7" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2206,13 +2317,13 @@
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="23" t="n">
+      <c r="H8" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2231,13 +2342,13 @@
       <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="H9" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2256,13 +2367,13 @@
       <c r="E10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2281,13 +2392,13 @@
       <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="23" t="n">
+      <c r="H11" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2297,27 +2408,27 @@
           <t>Median</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="23">
         <f>MEDIAN(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="23">
         <f>MEDIAN(D5:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="23">
         <f>MEDIAN(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="26">
         <f>MEDIAN(F5:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="26">
         <f>MEDIAN(G5:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="26">
         <f>MEDIAN(H5:H12)</f>
         <v/>
       </c>
@@ -2354,172 +2465,172 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>WACC \ Term. growth</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="28" t="n">
         <v>0.015</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="28" t="n">
         <v>0.025</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="28" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="28" t="n">
         <v>0.08</v>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="28" t="n">
         <v>0.09</v>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="28" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="28" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
@@ -2583,94 +2694,94 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>External historical evidence materialization</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>Generated public case equity-public-tesla-2020-offering from canonical release template</t>
-        </is>
-      </c>
-      <c r="E5" s="27" t="inlineStr">
-        <is>
-          <t>External historical case; human stakeholder approval remains pending</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="inlineStr">
-        <is>
-          <t>On source revision, builder change, monitoring breach, or annual review</t>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>Historical actuals block filled after the BASE template fix</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>The BASE template's income-statement historical block carried no input marker and no derived formulas, so the income statement, the DCF, and diluted EPS all evaluated to zero. With the template fixed, this fills FY2017-FY2019 revenue, cost of revenue, operating expense, depreciation and amortisation, interest, tax, and share count. Depreciation comes from the cash flow statement rather than EDGAR, because Tesla tagged EDGAR's D&amp;A concept in one filing only and with a narrower figure. With D&amp;A real and taken out of the operating expense row, the EBITDA line is a real EBITDA and EBIT ties exactly to the disclosed operating income in all three years.</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>External historical case; human stakeholder approval remains pending. Read three things before using any number here. First, the share counts are period-end outstanding rather than weighted diluted, which understates earnings per share. Second, the forward D&amp;A driver is the product of a capex ratio and a D&amp;A-to-capex ratio, and the second of those is unstable across the window; the pair is set so the product ties to D&amp;A as a share of revenue, which is stable, and the two rows must be read together. Third, the discounted cash flow values the equity at roughly a quarter of the price the February 2020 offering actually cleared at. That is not a defect in the arithmetic. It is what a cash flow model built on Tesla's FY2019 operating margins produces, and the gap between the two was the whole argument about Tesla at the time. The case exists to show the offering mechanics, not to settle that argument.</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>On builder change or annual review</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2694,125 +2805,125 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>Equity Finance — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>Equity Finance</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>tools/builders/build_equity_finance_release.py</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>issuer board, ECM, shareholders, counsel and exchange</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>capital raise and dilution memo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="42" t="inlineStr">
         <is>
           <t>daily during offering; quarterly cap table</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="D13" s="44" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="43" t="inlineStr">
+      <c r="E13" s="44" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="43" t="inlineStr">
+      <c r="F13" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2894,34 +3005,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="43" t="inlineStr">
+      <c r="B21" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="44" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="43" t="inlineStr">
+      <c r="E21" s="44" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="43" t="inlineStr">
+      <c r="F21" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3003,34 +3114,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="43" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="43" t="inlineStr">
+      <c r="D29" s="44" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="43" t="inlineStr">
+      <c r="E29" s="44" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="43" t="inlineStr">
+      <c r="F29" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3112,34 +3223,34 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="43" t="inlineStr">
+      <c r="B37" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="C37" s="44" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="43" t="inlineStr">
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="43" t="inlineStr">
+      <c r="E37" s="44" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="43" t="inlineStr">
+      <c r="F37" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3221,34 +3332,34 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="42" t="inlineStr">
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="43" t="inlineStr">
+      <c r="B45" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="43" t="inlineStr">
+      <c r="C45" s="44" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
+      <c r="D45" s="44" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="43" t="inlineStr">
+      <c r="E45" s="44" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="43" t="inlineStr">
+      <c r="F45" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3330,34 +3441,34 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="42" t="inlineStr">
+      <c r="B52" s="43" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="43" t="inlineStr">
+      <c r="B53" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="43" t="inlineStr">
+      <c r="C53" s="44" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
+      <c r="D53" s="44" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="43" t="inlineStr">
+      <c r="E53" s="44" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="43" t="inlineStr">
+      <c r="F53" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3439,34 +3550,34 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="42" t="inlineStr">
+      <c r="B60" s="43" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="43" t="inlineStr">
+      <c r="B61" s="44" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="43" t="inlineStr">
+      <c r="C61" s="44" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="43" t="inlineStr">
+      <c r="E61" s="44" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="43" t="inlineStr">
+      <c r="F61" s="44" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
@@ -3578,49 +3689,49 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
@@ -3723,54 +3834,54 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3947,20 +4058,20 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>0</v>
+      <c r="C5" s="46" t="n">
+        <v>0.445733</v>
+      </c>
+      <c r="D5" s="46" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="E5" s="46" t="n">
+        <v>0.295487</v>
+      </c>
+      <c r="F5" s="46" t="n">
+        <v>0.220363</v>
+      </c>
+      <c r="G5" s="46" t="n">
+        <v>0.14524</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
@@ -3974,20 +4085,20 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>0</v>
+      <c r="C6" s="46" t="n">
+        <v>0.165555</v>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>0.165555</v>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>0.165555</v>
+      </c>
+      <c r="F6" s="46" t="n">
+        <v>0.165555</v>
+      </c>
+      <c r="G6" s="46" t="n">
+        <v>0.165555</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -4001,20 +4112,20 @@
           <t>Opex % of revenue</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>0</v>
+      <c r="C7" s="46" t="n">
+        <v>0.080723</v>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>0.080723</v>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>0.080723</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>0.080723</v>
+      </c>
+      <c r="G7" s="46" t="n">
+        <v>0.080723</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -4028,20 +4139,20 @@
           <t>Tax rate %</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>0</v>
+      <c r="C8" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E8" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F8" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G8" s="46" t="n">
+        <v>0.21</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
@@ -4055,20 +4166,20 @@
           <t>D&amp;A % of capex</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>0</v>
+      <c r="C9" s="46" t="n">
+        <v>1.498956</v>
+      </c>
+      <c r="D9" s="46" t="n">
+        <v>1.498956</v>
+      </c>
+      <c r="E9" s="46" t="n">
+        <v>1.498956</v>
+      </c>
+      <c r="F9" s="46" t="n">
+        <v>1.498956</v>
+      </c>
+      <c r="G9" s="46" t="n">
+        <v>1.498956</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
@@ -4082,20 +4193,20 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>0</v>
+      <c r="C10" s="46" t="n">
+        <v>0.058467</v>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>0.058467</v>
+      </c>
+      <c r="E10" s="46" t="n">
+        <v>0.058467</v>
+      </c>
+      <c r="F10" s="46" t="n">
+        <v>0.058467</v>
+      </c>
+      <c r="G10" s="46" t="n">
+        <v>0.058467</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
@@ -4109,20 +4220,20 @@
           <t>NWC % of revenue chg</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>0</v>
+      <c r="C11" s="46" t="n">
+        <v>0.470816</v>
+      </c>
+      <c r="D11" s="46" t="n">
+        <v>0.470816</v>
+      </c>
+      <c r="E11" s="46" t="n">
+        <v>0.470816</v>
+      </c>
+      <c r="F11" s="46" t="n">
+        <v>0.470816</v>
+      </c>
+      <c r="G11" s="46" t="n">
+        <v>0.470816</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
@@ -4136,23 +4247,23 @@
           <t>Shares outstanding (mm)</t>
         </is>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="30">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="30">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="30">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="30">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="30">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
@@ -4168,20 +4279,20 @@
           <t>WACC %</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>0</v>
+      <c r="C13" s="46" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="D13" s="46" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="E13" s="46" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="F13" s="46" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>0.095</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -4195,20 +4306,20 @@
           <t>Terminal growth %</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>0</v>
+      <c r="C14" s="46" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E14" s="46" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F14" s="46" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>0.025</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
@@ -4251,7 +4362,7 @@
           <t>Active scenario</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
@@ -4290,13 +4401,13 @@
           <t>Existing common shares</t>
         </is>
       </c>
-      <c r="C5" s="45" t="n">
+      <c r="C5" s="47" t="n">
         <v>179.7</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="33">
         <f>IF($C$3="Adversarial",D5,C5)</f>
         <v/>
       </c>
@@ -4312,13 +4423,13 @@
           <t>In-the-money options / RSUs</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="33">
         <f>IF($C$3="Adversarial",D6,C6)</f>
         <v/>
       </c>
@@ -4334,13 +4445,13 @@
           <t>Primary shares issued</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="47" t="n">
         <v>2.65</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="32" t="n">
         <v>150</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="33">
         <f>IF($C$3="Adversarial",D7,C7)</f>
         <v/>
       </c>
@@ -4356,13 +4467,13 @@
           <t>Rights shares issued</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="33">
         <f>IF($C$3="Adversarial",D8,C8)</f>
         <v/>
       </c>
@@ -4378,13 +4489,13 @@
           <t>Convertible principal</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="17">
         <f>IF($C$3="Adversarial",D9,C9)</f>
         <v/>
       </c>
@@ -4400,13 +4511,13 @@
           <t>Conversion price</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="35">
         <f>IF($C$3="Adversarial",D10,C10)</f>
         <v/>
       </c>
@@ -4422,13 +4533,13 @@
           <t>Primary issue price</t>
         </is>
       </c>
-      <c r="C11" s="46" t="n">
+      <c r="C11" s="48" t="n">
         <v>767</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="35">
         <f>IF($C$3="Adversarial",D11,C11)</f>
         <v/>
       </c>
@@ -4444,13 +4555,13 @@
           <t>Transaction fees</t>
         </is>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="49" t="n">
         <v>40.6</v>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="17">
         <f>IF($C$3="Adversarial",D12,C12)</f>
         <v/>
       </c>
@@ -4472,7 +4583,7 @@
       <c r="D13" s="8" t="n">
         <v>0.35</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="36">
         <f>IF($C$3="Adversarial",D13,C13)</f>
         <v/>
       </c>
@@ -4494,7 +4605,7 @@
       <c r="D14" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>IF($C$3="Adversarial",D14,C14)</f>
         <v/>
       </c>
@@ -4505,7 +4616,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Derived outputs</t>
         </is>
@@ -4517,15 +4628,15 @@
           <t>Converted shares</t>
         </is>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="33">
         <f>IFERROR(C9/C10,0)</f>
         <v/>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="33">
         <f>IFERROR(D9/D10,0)</f>
         <v/>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="33">
         <f>IFERROR(E9/E10,0)</f>
         <v/>
       </c>
@@ -4536,15 +4647,15 @@
           <t>Fully diluted post-money shares</t>
         </is>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="33">
         <f>SUM(C5:C8)+C18</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="33">
         <f>SUM(D5:D8)+D18</f>
         <v/>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="33">
         <f>SUM(E5:E8)+E18</f>
         <v/>
       </c>
@@ -4555,15 +4666,15 @@
           <t>Existing common ownership</t>
         </is>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="36">
         <f>IFERROR(C5/C19,0)</f>
         <v/>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="36">
         <f>IFERROR(D5/D19,0)</f>
         <v/>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="36">
         <f>IFERROR(E5/E19,0)</f>
         <v/>
       </c>
@@ -4574,15 +4685,15 @@
           <t>Existing-holder dilution</t>
         </is>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="36">
         <f>1-C20</f>
         <v/>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="36">
         <f>1-D20</f>
         <v/>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="36">
         <f>1-E20</f>
         <v/>
       </c>
@@ -4593,15 +4704,15 @@
           <t>Option / RSU overhang</t>
         </is>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="36">
         <f>IFERROR(C6/C19,0)</f>
         <v/>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="36">
         <f>IFERROR(D6/D19,0)</f>
         <v/>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="36">
         <f>IFERROR(E6/E19,0)</f>
         <v/>
       </c>
@@ -4612,15 +4723,15 @@
           <t>Gross primary proceeds</t>
         </is>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="17">
         <f>C7*C11</f>
         <v/>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="17">
         <f>D7*D11</f>
         <v/>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="17">
         <f>E7*E11</f>
         <v/>
       </c>
@@ -4631,15 +4742,15 @@
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="17">
         <f>C23-C12</f>
         <v/>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="17">
         <f>D23-D12</f>
         <v/>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="17">
         <f>E23-E12</f>
         <v/>
       </c>
@@ -4650,21 +4761,21 @@
           <t>Share-conservation residual</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="33">
         <f>C19-C5-C6-C7-C8-C18</f>
         <v/>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="33">
         <f>D19-D5-D6-D7-D8-D18</f>
         <v/>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="33">
         <f>E19-E5-E6-E7-E8-E18</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>The fully diluted denominator must use the security-specific treasury-stock, if-converted, contingently issuable, and anti-dilution conventions approved for the analysis.</t>
         </is>
@@ -4726,11 +4837,11 @@
           <t>Existing shares entitled</t>
         </is>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="33">
         <f>'Cap Table &amp; Dilution'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="33">
         <f>'Cap Table &amp; Dilution'!D5</f>
         <v/>
       </c>
@@ -4746,11 +4857,11 @@
           <t>Rights shares offered</t>
         </is>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="33">
         <f>'Cap Table &amp; Dilution'!C8</f>
         <v/>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="33">
         <f>'Cap Table &amp; Dilution'!D8</f>
         <v/>
       </c>
@@ -4766,10 +4877,10 @@
           <t>Cum-rights market price</t>
         </is>
       </c>
-      <c r="C7" s="46" t="n">
+      <c r="C7" s="48" t="n">
         <v>767</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="34" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -4784,10 +4895,10 @@
           <t>Subscription price</t>
         </is>
       </c>
-      <c r="C8" s="46" t="n">
+      <c r="C8" s="48" t="n">
         <v>767</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="34" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -4802,10 +4913,10 @@
           <t>Expected participation</t>
         </is>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -4820,7 +4931,7 @@
           <t>Standby / backstop fee</t>
         </is>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="46" t="n">
         <v>0.01176</v>
       </c>
       <c r="D10" s="8" t="n">
@@ -4838,11 +4949,11 @@
           <t>Theoretical ex-rights price</t>
         </is>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="17">
         <f>IFERROR((C5*C7+C6*C8)/(C5+C6),0)</f>
         <v/>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="17">
         <f>IFERROR((D5*D7+D6*D8)/(D5+D6),0)</f>
         <v/>
       </c>
@@ -4853,11 +4964,11 @@
           <t>Theoretical value per right / existing share</t>
         </is>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="17">
         <f>C7-C13</f>
         <v/>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="17">
         <f>D7-D13</f>
         <v/>
       </c>
@@ -4868,11 +4979,11 @@
           <t>Subscription discount</t>
         </is>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>IFERROR(1-C8/C7,0)</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>IFERROR(1-D8/D7,0)</f>
         <v/>
       </c>
@@ -4883,11 +4994,11 @@
           <t>Expected subscribed shares</t>
         </is>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="33">
         <f>C6*C9</f>
         <v/>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="33">
         <f>D6*D9</f>
         <v/>
       </c>
@@ -4898,11 +5009,11 @@
           <t>Expected gross proceeds</t>
         </is>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="17">
         <f>C16*C8</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="17">
         <f>D16*D8</f>
         <v/>
       </c>
@@ -4913,11 +5024,11 @@
           <t>Expected standby fee</t>
         </is>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="17">
         <f>(C6-C16)*C8*C10</f>
         <v/>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="17">
         <f>(D6-D16)*D8*D10</f>
         <v/>
       </c>
@@ -4928,17 +5039,17 @@
           <t>Expected net rights proceeds</t>
         </is>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="17">
         <f>C17-C18</f>
         <v/>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="17">
         <f>D17-D18</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>TERP is a frictionless reference. Actual value depends on trading, eligibility, taxes, participation, backstop terms, execution leakage, and the use of proceeds.</t>
         </is>
@@ -5000,11 +5111,11 @@
           <t>Principal</t>
         </is>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="17">
         <f>'Cap Table &amp; Dilution'!C9</f>
         <v/>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="17">
         <f>'Cap Table &amp; Dilution'!D9</f>
         <v/>
       </c>
@@ -5020,11 +5131,11 @@
           <t>Conversion price</t>
         </is>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="35">
         <f>'Cap Table &amp; Dilution'!C10</f>
         <v/>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="35">
         <f>'Cap Table &amp; Dilution'!D10</f>
         <v/>
       </c>
@@ -5040,10 +5151,10 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="34" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -5076,10 +5187,10 @@
           <t>Remaining tenor</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="36" t="n">
+      <c r="D9" s="37" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -5112,10 +5223,10 @@
           <t>Anti-dilution adjusted price</t>
         </is>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="34" t="n">
         <v>9.5</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="34" t="n">
         <v>3.5</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -5130,11 +5241,11 @@
           <t>Contractual converted shares</t>
         </is>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="33">
         <f>IFERROR(C5/C6,0)</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="33">
         <f>IFERROR(D5/D6,0)</f>
         <v/>
       </c>
@@ -5145,11 +5256,11 @@
           <t>Anti-dilution adjusted shares</t>
         </is>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="33">
         <f>IFERROR(C5/C11,0)</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="33">
         <f>IFERROR(D5/D11,0)</f>
         <v/>
       </c>
@@ -5160,11 +5271,11 @@
           <t>Conversion value</t>
         </is>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="17">
         <f>C14*C7</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="17">
         <f>D14*D7</f>
         <v/>
       </c>
@@ -5175,11 +5286,11 @@
           <t>Redemption value</t>
         </is>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="17">
         <f>C5*(1+C10)</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="17">
         <f>D5*(1+D10)</f>
         <v/>
       </c>
@@ -5190,11 +5301,11 @@
           <t>Conversion parity</t>
         </is>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="38">
         <f>IFERROR(C16/C5,0)</f>
         <v/>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="38">
         <f>IFERROR(D16/D5,0)</f>
         <v/>
       </c>
@@ -5205,11 +5316,11 @@
           <t>Incremental anti-dilution shares</t>
         </is>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="33">
         <f>C15-C14</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="33">
         <f>D15-D14</f>
         <v/>
       </c>
@@ -5220,17 +5331,17 @@
           <t>Annual cash coupon</t>
         </is>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="17">
         <f>C5*C8</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="17">
         <f>D5*D8</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>This sheet models if-converted economics, not the full value of optionality. Call features, soft calls, resets, make-wholes, caps, floors, and settlement elections require explicit terms.</t>
         </is>
@@ -5292,11 +5403,11 @@
           <t>Share-conservation residual</t>
         </is>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>'Cap Table &amp; Dilution'!E25</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>IF(ABS(C5)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5312,11 +5423,11 @@
           <t>Ownership / dilution identity</t>
         </is>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="29">
         <f>'Cap Table &amp; Dilution'!E20+'Cap Table &amp; Dilution'!E21-1</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="29">
         <f>IF(ABS(C6)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5332,11 +5443,11 @@
           <t>Existing-holder dilution</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="29">
         <f>'Cap Table &amp; Dilution'!E21</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <f>IF(C7&lt;='Cap Table &amp; Dilution'!E13,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -5352,11 +5463,11 @@
           <t>Option / RSU overhang</t>
         </is>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="29">
         <f>'Cap Table &amp; Dilution'!E22</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>IF(C8&lt;='Cap Table &amp; Dilution'!E14,"PASS","REVIEW")</f>
         <v/>
       </c>
@@ -5372,11 +5483,11 @@
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="29">
         <f>'Cap Table &amp; Dilution'!E24</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="29">
         <f>IF(C9&gt;=0,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -5392,11 +5503,11 @@
           <t>Rights TERP residual</t>
         </is>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="29">
         <f>'Rights Offering'!C13-(('Rights Offering'!C5*'Rights Offering'!C7+'Rights Offering'!C6*'Rights Offering'!C8)/('Rights Offering'!C5+'Rights Offering'!C6))</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <f>IF(ABS(C10)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5412,11 +5523,11 @@
           <t>Rights value</t>
         </is>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="29">
         <f>'Rights Offering'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="29">
         <f>IF(C11&gt;=0,"PASS","REVIEW")</f>
         <v/>
       </c>
@@ -5432,11 +5543,11 @@
           <t>Adversarial rights participation</t>
         </is>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="29">
         <f>'Rights Offering'!D9</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="29">
         <f>IF(C12&gt;=0.75,"PASS",IF(C12&gt;=0.50,"REVIEW","BREACH"))</f>
         <v/>
       </c>
@@ -5452,11 +5563,11 @@
           <t>Converted-share reconciliation</t>
         </is>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="29">
         <f>'Convertible Securities'!C14-'Cap Table &amp; Dilution'!C18</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="29">
         <f>IF(ABS(C13)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5472,11 +5583,11 @@
           <t>Incremental anti-dilution shares</t>
         </is>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="29">
         <f>'Convertible Securities'!D19</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="29">
         <f>IF(C14&lt;=0,"PASS","REVIEW")</f>
         <v/>
       </c>
@@ -5492,13 +5603,13 @@
           <t>Overall model status</t>
         </is>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <f>IF(COUNTIF(D5:D14,"FAIL")+COUNTIF(D5:D14,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D14,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Primary decision outputs</t>
         </is>
@@ -5510,7 +5621,7 @@
           <t>Fully diluted shares</t>
         </is>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="33">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
@@ -5521,7 +5632,7 @@
           <t>Existing-holder dilution</t>
         </is>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="36">
         <f>'Cap Table &amp; Dilution'!E21</f>
         <v/>
       </c>
@@ -5532,7 +5643,7 @@
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="17">
         <f>'Cap Table &amp; Dilution'!E24</f>
         <v/>
       </c>
@@ -5543,7 +5654,7 @@
           <t>Base TERP</t>
         </is>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="35">
         <f>'Rights Offering'!C13</f>
         <v/>
       </c>
@@ -5554,7 +5665,7 @@
           <t>Expected net rights proceeds</t>
         </is>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="17">
         <f>'Rights Offering'!C19</f>
         <v/>
       </c>
@@ -5565,7 +5676,7 @@
           <t>Contractual converted shares</t>
         </is>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="33">
         <f>'Convertible Securities'!C14</f>
         <v/>
       </c>
@@ -5576,7 +5687,7 @@
           <t>Adversarial anti-dilution shares</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="33">
         <f>'Convertible Securities'!D15</f>
         <v/>
       </c>
@@ -5587,7 +5698,7 @@
           <t>Adversarial redemption value</t>
         </is>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="17">
         <f>'Convertible Securities'!D17</f>
         <v/>
       </c>
